--- a/results/Int Task Remove ACC 0.7/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.7/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000393517350864698</v>
+        <v>3.006767258528211e-05</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.001133002841017703</v>
+        <v>-0.002144397801606522</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0007715360563415486</v>
+        <v>7.624085694785557e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0004311223475067294</v>
+        <v>0.0004129929463951354</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.00144275866070571</v>
+        <v>0.0003959834443221089</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001419987245889648</v>
+        <v>0.002363259716306478</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.696443837753026e-05</v>
+        <v>0.0001277789397363671</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.76576626617076e-05</v>
+        <v>0.000923606156002057</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01189377598007735</v>
+        <v>0.008148583466061659</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008229947544100644</v>
+        <v>0.009645632326954149</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002508776907463449</v>
+        <v>0.0009274191502229344</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005652958325504876</v>
+        <v>-0.0007469252152498706</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0007398973048624767</v>
+        <v>-0.001621211394746535</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009720426246392407</v>
+        <v>0.009533919544178461</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004312759639004663</v>
+        <v>0.005060086340620079</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0006169153836085196</v>
+        <v>0.0006297610001542465</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.002321150073290468</v>
+        <v>-0.001025233193195674</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001515972001897916</v>
+        <v>0.00370693582282568</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001043413601021158</v>
+        <v>0.0003676115916803911</v>
       </c>
       <c r="V3" t="n">
-        <v>1.347037573330101e-05</v>
+        <v>7.397721926518662e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002347052304256836</v>
+        <v>0.001691112033405215</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001588327012375701</v>
+        <v>0.0006641679278595202</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001037680924189489</v>
+        <v>-0.0006712244817026891</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0004061615416463738</v>
+        <v>0.001025169807170345</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00100603681642165</v>
+        <v>0.001167951342592725</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0001609065584864944</v>
+        <v>0.0001942248229613231</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.002943758822395811</v>
+        <v>0.003571249196233041</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.0003628905110809668</v>
+        <v>1.98358319463689e-05</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.000667074545919043</v>
+        <v>-0.0005341128782535042</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0009382312979732965</v>
+        <v>-0.0002425167027415775</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.000104653484824333</v>
+        <v>-2.985721053268666e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0004028515027655255</v>
+        <v>0.0001292182318060675</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0009961458445755566</v>
+        <v>0.001028468487946246</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.000193566299464677</v>
+        <v>-0.000332867647149494</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0001556298353681884</v>
+        <v>-0.0001711009341863434</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.000308398673828767</v>
+        <v>-9.464492985409968e-05</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0001481464872659576</v>
+        <v>0.0008755819796116305</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0002980063571065906</v>
+        <v>0.0007810845250355958</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0001786036441106753</v>
+        <v>0.0001568048987260794</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0002009783491293471</v>
+        <v>0.0008459343119760886</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.000738359012698957</v>
+        <v>0.0009275884462288618</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0005922210254000848</v>
+        <v>0.0008354456698952585</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0009067152134265586</v>
+        <v>-0.000409105919683792</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.004037918642694678</v>
+        <v>-0.001698236946256473</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0004131030847141303</v>
+        <v>-0.00066612271874674</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0002019203734203101</v>
+        <v>-0.0006012456833917379</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0003006481958576934</v>
+        <v>-0.0002207379131700305</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.0001402642613389914</v>
+        <v>-0.0007856351807471861</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0003948355756365972</v>
+        <v>-0.000191281259362922</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0004970262867130184</v>
+        <v>-0.004149710100740984</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0004037140886913304</v>
+        <v>0.003470302951303628</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0003835109849061158</v>
+        <v>-0.000241248525953851</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.684498054354669e-05</v>
+        <v>-4.662988687554215e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.00087997131967381</v>
+        <v>6.369306024734616e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.0008728123746779536</v>
+        <v>0.001210907690170534</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.0007651722910137281</v>
+        <v>-0.001351909185886771</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-2.552140974714121e-05</v>
+        <v>-0.0002960884462093316</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.0007857633811229125</v>
+        <v>0.0004617187610086637</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.001496803503172968</v>
+        <v>-0.0004278650881770683</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0002988534607978388</v>
+        <v>-0.0002178684670014585</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.00100640179677654</v>
+        <v>0.000234208744655784</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0005950511833122495</v>
+        <v>0.0003922540186238667</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.00440871665935856</v>
+        <v>-0.001562408605073514</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.001566798431589587</v>
+        <v>0.0009902792407667916</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.0001514727138445382</v>
+        <v>-6.425420402389476e-07</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.0003120339987590048</v>
+        <v>-0.0004995305406906822</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0006515991861443937</v>
+        <v>0.001796856205585287</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0008101141251522935</v>
+        <v>0.0009889206187374288</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.002214141740902422</v>
+        <v>0.0001792586247992078</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.001163452284685748</v>
+        <v>-6.109235195385634e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.001467220153041525</v>
+        <v>0.001920213896570363</v>
       </c>
       <c r="BX3" t="n">
-        <v>-1.069468314181865e-05</v>
+        <v>-1.632819625883574e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.156165719706562e-05</v>
+        <v>0.0005343956124113957</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0001907974109947286</v>
+        <v>0.0003434953400115304</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0002179140044926154</v>
+        <v>-9.007747020499665e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.001261743690263715</v>
+        <v>0.002289336595204281</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>5.277044854881119e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>9.350550539640176e-05</v>
+        <v>7.069063137333354e-05</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0007640003351926782</v>
+        <v>0.0004938661661223586</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0005097661422291987</v>
+        <v>0.001930733366192857</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0001289694561731991</v>
+        <v>0.0001322017608243298</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0001057399368322864</v>
+        <v>0.00144151883688273</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.001618738866800801</v>
+        <v>0.001625902913292164</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0005084206292079154</v>
+        <v>0.0007988424271410211</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005774440029246034</v>
+        <v>0.00502924947783594</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009745541481627523</v>
+        <v>0.007058683497352229</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004913943596544097</v>
+        <v>0.003779721904971608</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002415191900723609</v>
+        <v>0.001547234067319991</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003617382498983402</v>
+        <v>0.003728952416340947</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008243248771063165</v>
+        <v>0.005177651988790227</v>
       </c>
       <c r="I4" t="n">
-        <v>4.474375999404722e-05</v>
+        <v>0.0001844731144188187</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007507722904653858</v>
+        <v>0.003980651935546442</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01149894060152963</v>
+        <v>0.009964031082302508</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01080265328806199</v>
+        <v>0.0126243279385772</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00598820683406681</v>
+        <v>0.004289682209412962</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003277857963522809</v>
+        <v>0.003384139520744316</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002813734236178952</v>
+        <v>0.00548107668324497</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0103223315612216</v>
+        <v>0.01008296670363569</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01141315781403267</v>
+        <v>0.007624413374020951</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003050440585257325</v>
+        <v>0.00436641164054079</v>
       </c>
       <c r="S4" t="n">
-        <v>0.006718124581183643</v>
+        <v>0.004487821264133774</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004193554762404635</v>
+        <v>0.004006490483109125</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006433421022152366</v>
+        <v>0.004488504302767353</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0002041881093824425</v>
+        <v>7.496248650624785e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00768664481445486</v>
+        <v>0.004047403290439571</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003625506279184371</v>
+        <v>0.003986073991654374</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001885746403511781</v>
+        <v>0.002504552805243378</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001507799492688729</v>
+        <v>0.00264720981920807</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001281769810849006</v>
+        <v>0.003153088819947354</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003411997574064652</v>
+        <v>0.0004106153634178864</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.004712151843652488</v>
+        <v>0.003887982332140696</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004669406914360965</v>
+        <v>0.003401142138752803</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.002516098407569165</v>
+        <v>0.003551977080542826</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.002295171717353396</v>
+        <v>0.002881473516826332</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0003445003263265105</v>
+        <v>0.0006061200952491702</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0007445751365750043</v>
+        <v>0.0006412828400946266</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.003068134235613907</v>
+        <v>0.003364973535861168</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.002423968345100886</v>
+        <v>0.003874172264800817</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0003115010443545238</v>
+        <v>0.0002844012438197752</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0009096089668873491</v>
+        <v>0.0006093841845662424</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002859612991011967</v>
+        <v>0.003342690725173474</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.001169801033008835</v>
+        <v>0.003583554172148611</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0005319138334764046</v>
+        <v>0.0008865266328084799</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002321054850577542</v>
+        <v>0.002555677845985565</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.001714938733123536</v>
+        <v>0.004172891511655684</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001836956445300772</v>
+        <v>0.002708829908506585</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.002952527590666575</v>
+        <v>0.002950125273221484</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.009747461996018565</v>
+        <v>0.01070762909952526</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.003340320135560013</v>
+        <v>0.001544798493672948</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.00380200461302015</v>
+        <v>0.00371842221213134</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0004331903765639255</v>
+        <v>0.0003509342616127501</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.004838692829282899</v>
+        <v>0.005776317323307169</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.00392782675632222</v>
+        <v>0.0028506939123799</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.007076764002812709</v>
+        <v>0.006604777353988984</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.006456405622645562</v>
+        <v>0.008060366305622872</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0007412481491501923</v>
+        <v>0.0005958207705509759</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0002954097076945335</v>
+        <v>0.00100932290414221</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.00253616646011802</v>
+        <v>0.006379556227707081</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.009778894076053812</v>
+        <v>0.009395332523018801</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.004005266010764555</v>
+        <v>0.003547965257538059</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0003642746280444048</v>
+        <v>0.0005759051680969861</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001504568780925034</v>
+        <v>0.00283810709338026</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.003579926518489903</v>
+        <v>0.004449059026969997</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0003157946088724482</v>
+        <v>0.0006335309405778744</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.002805999179156786</v>
+        <v>0.005136467141057859</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.004117958420076379</v>
+        <v>0.008074655681283136</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.01153152650888288</v>
+        <v>0.0108648594165547</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.004861805864337383</v>
+        <v>0.003067689661975488</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0003251015329638053</v>
+        <v>4.78405949334906e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.003143275951021234</v>
+        <v>0.002894459113006261</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.004191886595237296</v>
+        <v>0.003401716561838101</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001651758173149744</v>
+        <v>0.002325871554027215</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.006211433839018383</v>
+        <v>0.001418476695327775</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.004641182155418587</v>
+        <v>0.002701680142619126</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.007213620574614277</v>
+        <v>0.005067476988223068</v>
       </c>
       <c r="BX4" t="n">
-        <v>4.188724884473999e-05</v>
+        <v>0.000196883049020185</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0003853638608215832</v>
+        <v>0.0008430614274199205</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0007388773794501562</v>
+        <v>0.0005038269156249333</v>
       </c>
       <c r="CA4" t="n">
         <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001076305242008234</v>
+        <v>0.0004666922847384296</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.007463047114796583</v>
+        <v>0.004529053759191251</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>0.0001668748105629705</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001133726609739415</v>
+        <v>0.0005890040904873605</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.005081603558441149</v>
+        <v>0.001673157220513876</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.003801545540887612</v>
+        <v>0.004035685767678139</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0006317504984224726</v>
+        <v>0.0003511644517110348</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.003019603065695475</v>
+        <v>0.003762687618772788</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.007196687917809835</v>
+        <v>0.005116162043734202</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002379409040982098</v>
+        <v>0.001403244265351456</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.008501594048884098</v>
+        <v>-0.008342189160467606</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02636815920398009</v>
+        <v>-0.02023217247097846</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.007168674698795186</v>
+        <v>-0.006535600425079724</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.005361445783132524</v>
+        <v>-0.001530343007915591</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.007349397590361429</v>
+        <v>-0.007131011608623628</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01609989373007435</v>
+        <v>-0.004197662061636576</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0001068947087119243</v>
+        <v>-6.024096385540689e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01323060573857593</v>
+        <v>-0.008182784272051014</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0002672367717798108</v>
+        <v>-0.006734366648850831</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.002308447937131608</v>
+        <v>-0.008551576696953467</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.007352128247650603</v>
+        <v>-0.005583195135434027</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.003316749585406287</v>
+        <v>-0.008551576696953445</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.005791710945802264</v>
+        <v>-0.01408076514346444</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.009037328094302532</v>
+        <v>-0.01041257367387031</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01704970603955107</v>
+        <v>-0.007482629609834268</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.002040816326530559</v>
+        <v>-0.007704569606801303</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01206163655685435</v>
+        <v>-0.008554729011689721</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.004638554216867474</v>
+        <v>-0.0001068947087119687</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0121679064824654</v>
+        <v>-0.007173219978746037</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0003719447396386633</v>
+        <v>-0.000180722891566254</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01987951807228917</v>
+        <v>-0.007409638554216824</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.004990118577075042</v>
+        <v>-0.006966403162055379</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.001277013752455769</v>
+        <v>-0.005184393372528007</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.002796833773087049</v>
+        <v>-0.004010554089709783</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.0006876227897838593</v>
+        <v>-0.001530343007915591</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0007858546168958314</v>
+        <v>-0.00024557956777993</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.001934770591487001</v>
+        <v>-0.0007858546168958425</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.009036144578313244</v>
+        <v>-0.005291288081239942</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.003433734939759048</v>
+        <v>-0.009733201581027705</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.003741314804917162</v>
+        <v>-0.003648424543947026</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0007411067193675569</v>
+        <v>-0.0008372579801150803</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001635883905013147</v>
+        <v>-0.001255886970172659</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.002351683591662213</v>
+        <v>-0.002405130946018142</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.003985122210414371</v>
+        <v>-0.004222340994120821</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0003952569169960119</v>
+        <v>-0.0006860158311345454</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.001265060240963856</v>
+        <v>-0.001216141514649083</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.004761904761904722</v>
+        <v>-0.002849604221635893</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.001753453772582292</v>
+        <v>-0.003606719367588984</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0003206841261357729</v>
+        <v>-0.001031434184675806</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.003819989534275215</v>
+        <v>-0.002062868369351622</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.002667984189723293</v>
+        <v>-0.004888416578108434</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.001002638522427413</v>
+        <v>-0.003746701846965717</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.00646712987707111</v>
+        <v>-0.003373493975903585</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.02121372031662266</v>
+        <v>-0.02255478353821482</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.006521739130434745</v>
+        <v>-0.004469548133595247</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01004709576138143</v>
+        <v>-0.009727418492784568</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001144578313253008</v>
+        <v>-0.0008433734939758741</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01198325484039763</v>
+        <v>-0.01151229722658291</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.006467661691542259</v>
+        <v>-0.007071240105540921</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.01240963855421688</v>
+        <v>-0.02131926121372033</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.008734939759036131</v>
+        <v>-0.007482629609834268</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.002124505928853715</v>
+        <v>-0.001185770750988169</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0003458498023715117</v>
+        <v>-0.00221635883905017</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.007598944591029011</v>
+        <v>-0.01187335092348285</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.01921686746987952</v>
+        <v>-0.01222891566265056</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01036144578313253</v>
+        <v>-0.007744636316064868</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.0005844845908607565</v>
+        <v>-0.001656867985034716</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.002878074306645673</v>
+        <v>-0.003081827842720519</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.002112313240597608</v>
+        <v>-0.006144578313252968</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0008840864440078144</v>
+        <v>-0.001487778958554764</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.007535321821036056</v>
+        <v>-0.01010154997327628</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.008373493975903612</v>
+        <v>-0.01298153034300793</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.03029023746701844</v>
+        <v>-0.0274934036939314</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.002598120508568258</v>
+        <v>-0.002173913043478315</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0006422924901185678</v>
+        <v>-0.0001046572475143837</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.004133961276818377</v>
+        <v>-0.004516471838469737</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.002717391304347761</v>
+        <v>-0.001375245579567741</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.004156626506024108</v>
+        <v>-0.001046572475143881</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.002825745682888481</v>
+        <v>-0.001779173207744611</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.002111984282907642</v>
+        <v>-0.005434782608695709</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.004199604743082941</v>
+        <v>-0.003931987247608959</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0001062699256110355</v>
+        <v>-0.0005313496280552332</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.0006376195536662799</v>
+        <v>-0.0005928853754940788</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.0006332453825857343</v>
+        <v>-5.232862375716962e-05</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.001372031662269091</v>
+        <v>-0.0009942438513866891</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.007262845849802324</v>
+        <v>-0.001669941060903679</v>
       </c>
       <c r="CD5" t="n">
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.001222104144527037</v>
+        <v>-0.001151229722658287</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.004199604743082941</v>
+        <v>-0.001339515713549788</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.003705533596837896</v>
+        <v>-0.002407116692830957</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0007739082365948002</v>
+        <v>-0.0004940711462450787</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.004891304347826031</v>
+        <v>-0.001391035548686315</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.004367053620784944</v>
+        <v>-0.003831041257367351</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.005180722891566259</v>
+        <v>-0.0007367387033398343</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002131405417941065</v>
+        <v>-0.00235079367163015</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.001508700926402726</v>
+        <v>-0.001219910924576259</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.002876377658001353</v>
+        <v>-0.001548060221488964</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001349560729507909</v>
+        <v>-0.000609701716563868</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.002453672709451843</v>
+        <v>-0.001165836149038438</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.00193049755867149</v>
+        <v>-0.001700677743293571</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.145936981757859e-05</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.003310189846952899</v>
+        <v>0.0004810261892036538</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003448057181153719</v>
+        <v>0.0007486937997164822</v>
       </c>
       <c r="L6" t="n">
-        <v>-8.110820618523193e-05</v>
+        <v>-0.001708987675301402</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0003206841261357563</v>
+        <v>-0.001854924610031442</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0008380471325011157</v>
+        <v>-0.001304786178894471</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001736041864435176</v>
+        <v>-0.004004583271621995</v>
       </c>
       <c r="P6" t="n">
-        <v>0.003443185415541608</v>
+        <v>0.004479268844736243</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.001236754813691107</v>
+        <v>0.0002819724644193444</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.001493134341828944</v>
+        <v>-0.001695408358521433</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.007719855795551617</v>
+        <v>-0.003182306339787003</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0001397520274060121</v>
+        <v>0.0005398733094535979</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0009163366839272879</v>
+        <v>-0.001985021861899774</v>
       </c>
       <c r="V6" t="n">
-        <v>-8.291873963515718e-05</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0004878954594566609</v>
+        <v>0.000226803428191058</v>
       </c>
       <c r="X6" t="n">
-        <v>-5.585675338024843e-05</v>
+        <v>-0.001108876407110984</v>
       </c>
       <c r="Y6" t="n">
-        <v>-8.326672684688675e-18</v>
+        <v>-0.001892564277782483</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.00134015828891601</v>
+        <v>-0.0003214191585139192</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.344735435595938e-05</v>
+        <v>-0.0003329631045247639</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0003299845298818576</v>
+        <v>-7.849293563576276e-05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0001708126228277179</v>
+        <v>0.0002590448150972341</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.002906209300645168</v>
+        <v>-0.001605376171404774</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.002318092912744954</v>
+        <v>-0.0009634046608668539</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.381978993919286e-05</v>
+        <v>-0.002030999465526456</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0002524775719794564</v>
+        <v>-0.0003214191585138887</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0008207697368164512</v>
+        <v>-0.0001583113456464336</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.0009922262054457703</v>
+        <v>-0.0007067957482039061</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.001328473782021236</v>
+        <v>-0.00385500500023809</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>-0.0003884092217810609</v>
       </c>
       <c r="AM6" t="n">
-        <v>-4.008551576697162e-05</v>
+        <v>-0.0005421686746987564</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0005831744974779506</v>
+        <v>-0.00229972221622512</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0002259036144578314</v>
+        <v>-0.001590058792089804</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0001833710955459644</v>
+        <v>-0.0005365705906663909</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.001002819953242667</v>
+        <v>-0.0010154997327632</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.002400145185350633</v>
+        <v>-0.001748927833192748</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0005211117049705977</v>
+        <v>-0.0008374589128626708</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.002434113741122895</v>
+        <v>-0.002982340084567023</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.009349835271176159</v>
+        <v>-0.006044521092284702</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001704316146554785</v>
+        <v>-0.0004908605060018862</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0009057200816286581</v>
+        <v>-0.001614088551200346</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0005120183444913661</v>
+        <v>-0.0004924302492447352</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0006280064136825469</v>
+        <v>-0.0008533594654844851</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.002020690544362094</v>
+        <v>-0.001369858055763137</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.001428751823880442</v>
+        <v>-0.004709004430848157</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.00375838733284912</v>
+        <v>-0.001878169556122455</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0007129087347643143</v>
+        <v>-0.0005521930737076769</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0002004275788348581</v>
+        <v>-0.0003468484380143272</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0006504699582971258</v>
+        <v>-0.0007421106372941383</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.004273648343453837</v>
+        <v>-0.005378294922005672</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.001538163676439558</v>
+        <v>-0.003130724613564321</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0002805986103688013</v>
+        <v>-0.0004683404918444239</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.002177378367139451</v>
+        <v>-0.001755246357063536</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.0006439014888605766</v>
+        <v>-0.003183400360382585</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0005128964316351486</v>
+        <v>-0.0006294825668094416</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.0004710611553643912</v>
+        <v>-0.001141413936027974</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.0002675491633302246</v>
+        <v>-0.003244857327299919</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.004317831107053633</v>
+        <v>-0.004510716509562218</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.0005244049681706886</v>
+        <v>-0.0007558422419141648</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.0004145936981757858</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001497050453317816</v>
+        <v>-0.002604654865767836</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001179713614692837</v>
+        <v>0.0001058722656913619</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0008275990707888092</v>
+        <v>0.0001761605929126137</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0006967499044073788</v>
+        <v>-0.0007437561880867333</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001162711016703877</v>
+        <v>-0.001394319215356538</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.0008923852740483739</v>
+        <v>-0.001566637481848476</v>
       </c>
       <c r="BX6" t="n">
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-7.367387033397065e-05</v>
+        <v>6.596306068603898e-05</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-9.278460014757738e-05</v>
+        <v>2.470355731224172e-05</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0001195536663124275</v>
+        <v>-0.0003357443670996274</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.00128245445157541</v>
+        <v>-0.0002498346934593887</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.000308503265334617</v>
+        <v>-9.0361445783127e-05</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0009967491399292179</v>
+        <v>-0.0004895527804592875</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.000617098790344553</v>
+        <v>-0.0002775684305702242</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0002803643167059722</v>
+        <v>0</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.001937996749251253</v>
+        <v>-0.0007529488961538239</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.0007643893332776874</v>
+        <v>-0.001657002264011481</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.001869158816806537</v>
+        <v>-0.0001569858712715422</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0002891416509092027</v>
+        <v>-4.911591355599154e-05</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.055607552680864e-05</v>
+        <v>2.050279153392731e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.001261480623166472</v>
+        <v>0.0001086134175635356</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0001613058226776043</v>
+        <v>0.0003070969071368223</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0004169774791407954</v>
+        <v>0.001299851007470887</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.000160342063067892</v>
+        <v>0.001375647080770431</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.672367717798108e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000914658603785523</v>
+        <v>0.001195066065898481</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008997551256028757</v>
+        <v>0.007120718880727372</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005189366430172005</v>
+        <v>0.01263521411276935</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001461966310718815</v>
+        <v>0.001444744494936245</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0004520650508281043</v>
+        <v>-0.000323098170735675</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0004186289900575346</v>
+        <v>-1.165860027086958e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.009566003791409039</v>
+        <v>0.01083709503969918</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003829841010219404</v>
+        <v>0.006149243089304497</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0002898196039268664</v>
+        <v>0.0002159938542741824</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.001084483458309482</v>
+        <v>-0.0007523243958263369</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0009045439338956962</v>
+        <v>0.002714501908973954</v>
       </c>
       <c r="U7" t="n">
-        <v>-3.443375405571826e-05</v>
+        <v>3.01996037603391e-05</v>
       </c>
       <c r="V7" t="n">
-        <v>2.470355731226115e-05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001147308072129966</v>
+        <v>0.002090264945785503</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00209693251712707</v>
+        <v>0.0003931450807919845</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0006593490007791358</v>
+        <v>-0.0003453772582359571</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.000169739977045974</v>
+        <v>0.0006011519405575317</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0005423180410274675</v>
+        <v>0.0003957970750745443</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>5.34473543559677e-05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.001371007874097397</v>
+        <v>0.003037888832005314</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.0005840658594766901</v>
+        <v>-5.873159987812012e-05</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0012231506313725</v>
+        <v>-5.715882206692724e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0009472171251289686</v>
+        <v>-0.0008646134287737083</v>
       </c>
       <c r="AG7" t="n">
-        <v>-2.4557956777993e-05</v>
+        <v>-5.313496280552888e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>0.0002798868161274281</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0004962256087380713</v>
+        <v>-7.396507140249308e-05</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.0005699024639647443</v>
+        <v>0.0003901506037608027</v>
       </c>
       <c r="AL7" t="n">
-        <v>7.970244420830164e-05</v>
+        <v>-2.47035573122556e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.551115123125783e-18</v>
+        <v>7.985863998348219e-05</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.0001597172799669977</v>
+        <v>0.001154639084417319</v>
       </c>
       <c r="AO7" t="n">
-        <v>5.436325705636124e-05</v>
+        <v>0.0001418812809196812</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>0.000133149798564236</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0001861019806361386</v>
+        <v>0.0001577897607475731</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.000744770478842871</v>
+        <v>0.0004162833044356884</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0002089706193752594</v>
+        <v>0.0006550267345068417</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.0009473156060798126</v>
+        <v>-0.0009102831199494456</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.00546600846084494</v>
+        <v>0.0009124600624901391</v>
       </c>
       <c r="AV7" t="n">
-        <v>-7.80053111339496e-05</v>
+        <v>-0.0002301300061907652</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.000303109206867841</v>
+        <v>0.0003470954117632541</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.0001630897711691004</v>
+        <v>-5.551115123125783e-18</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0002339519786264121</v>
+        <v>-0.0005952055756170637</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0004504474735867791</v>
+        <v>0.0009858126839419946</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0009718896172259573</v>
+        <v>-0.00293752771433925</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0007884011134800917</v>
+        <v>0.001671950585528503</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0.0002137894174238153</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.455795677800965e-05</v>
+        <v>7.411067193674459e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0001705324773170702</v>
+        <v>7.961166623456362e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.002807394682219305</v>
+        <v>0.002304920169653746</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0009480875231822672</v>
+        <v>-0.001771055926669957</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>5.402480415279132e-05</v>
+        <v>-0.0001599364072711662</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.0003938741212393682</v>
+        <v>-0.0001050629033111539</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.0001057759781131373</v>
+        <v>-0.001590465685013376</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.0002252535249429477</v>
+        <v>-5.142723449023667e-05</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.889488037380876e-05</v>
+        <v>0.0006602682939808757</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0007671555239700811</v>
+        <v>-0.001220112788705535</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.0009029819761434743</v>
+        <v>0.0003952868648481212</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0001292869450899237</v>
+        <v>-0.0001767247627477375</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.0003464706286624264</v>
+        <v>-0.0007882585384763941</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.0001964636542239495</v>
+        <v>0.0009513101023635173</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.0004543025120256783</v>
+        <v>0.0004348110284258244</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.0001078584683216422</v>
+        <v>0.0002613585003028607</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0001212809386008262</v>
+        <v>7.554239963621922e-05</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0.0002080068597655416</v>
+        <v>0.000273389790072981</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.616431187861812e-05</v>
+        <v>0.0003741314804916962</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.672367717798108e-05</v>
+        <v>0.000211810822708669</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>8.017103153393212e-05</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0001538449018679389</v>
+        <v>0.001136589243726832</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0</v>
+        <v>4.926151409024859e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0001593267043571489</v>
+        <v>0.0004275788348476695</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0001249555042899475</v>
+        <v>0.00130300323936059</v>
       </c>
       <c r="CH7" t="n">
-        <v>2.575991756826323e-05</v>
+        <v>2.45579567780152e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>-2.672367717798108e-05</v>
+        <v>-8.03272273091682e-05</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0.0003180034377847862</v>
+        <v>0.0001068947087118855</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0001316303480136727</v>
+        <v>0.0004535215331495812</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001593444081798168</v>
+        <v>0.001236476043276635</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001809630026702663</v>
+        <v>0.001013888744042451</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002374670184696753</v>
+        <v>0.001345183907592223</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001549664825235572</v>
+        <v>0.001457223518702888</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00014278498473356</v>
+        <v>0.003396424245073748</v>
       </c>
       <c r="H8" t="n">
-        <v>0.007135848914784554</v>
+        <v>0.005143472896828072</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.0002591689509772593</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00133866609768826</v>
+        <v>0.003320627405174795</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01673312678024328</v>
+        <v>0.0175878910900519</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01110223549537538</v>
+        <v>0.02064230299688887</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00403937748870084</v>
+        <v>0.004014087855366119</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0002688945940827525</v>
+        <v>-0.0001034440645833884</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00125175508529283</v>
+        <v>0.002093225829149844</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01735874294838246</v>
+        <v>0.01415686563350609</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0128019634949273</v>
+        <v>0.009332499389039168</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001513756356115739</v>
+        <v>0.002788224377352386</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00139610276233362</v>
+        <v>0.001598411741663983</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002159694053916872</v>
+        <v>0.005577009530659938</v>
       </c>
       <c r="U8" t="n">
-        <v>0.005079039038727695</v>
+        <v>0.003235722730166646</v>
       </c>
       <c r="V8" t="n">
-        <v>5.316767170627235e-05</v>
+        <v>4.933431435737435e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002702195872387575</v>
+        <v>0.003514480463296146</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003271923652679015</v>
+        <v>0.002738863114540713</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001522457431769575</v>
+        <v>0.0005075729031298909</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0003506501660007072</v>
+        <v>0.002741663170093328</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002170873254067465</v>
+        <v>0.001325750411378673</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.985122210415082e-05</v>
+        <v>0.0002993482964802841</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.003559618484850047</v>
+        <v>0.006188947312011034</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.003284960422163627</v>
+        <v>0.002438766053223912</v>
       </c>
       <c r="AE8" t="n">
-        <v>4.008551576697162e-05</v>
+        <v>0.001740974083452371</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002027777120268906</v>
+        <v>0.0007145477785405168</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.957783641160839e-05</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0001105108055009935</v>
+        <v>0.0004403927324272944</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001894009400478044</v>
+        <v>0.001581325301204842</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0009463213694932609</v>
+        <v>0.0009645866255674457</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0003689513150500701</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0007048973339369519</v>
+        <v>0.0002609718921626619</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0001337533888684711</v>
+        <v>0.002453195868049313</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.00107007406102825</v>
+        <v>0.003341474082873805</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0004236485114267247</v>
+        <v>0.0004800108304929329</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0003703866202569933</v>
+        <v>0.002664597028245666</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0005011500347619436</v>
+        <v>0.002610189742539756</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0005921765592906747</v>
+        <v>0.002351320705708407</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.00158760430896982</v>
+        <v>0.001728081430790698</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0007472992013737356</v>
+        <v>0.004608832415497036</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0003677848953774876</v>
+        <v>4.008551576694386e-05</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.002086736878836451</v>
+        <v>0.001093019683059895</v>
       </c>
       <c r="AX8" t="n">
-        <v>-2.672367717798108e-05</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001438212761907792</v>
+        <v>0.001667286482865038</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.003103164637441605</v>
+        <v>0.001501752693663236</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.002871630928126684</v>
+        <v>-0.0009974586255524776</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.002519696483701589</v>
+        <v>0.007057840609417304</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.145936981757859e-05</v>
+        <v>0.0002770448548812587</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0002255287619364277</v>
+        <v>0.0003144085374441413</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0004189159532477643</v>
+        <v>0.001041602959724783</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.004077757186345374</v>
+        <v>0.007362432477823525</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001432992269306016</v>
+        <v>0.0002845822233469575</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>9.23399936686442e-05</v>
+        <v>0.000102727016919979</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.0001931993817619743</v>
+        <v>0.001749523492433877</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.003153070989367741</v>
+        <v>0.001382178198274159</v>
       </c>
       <c r="BL8" t="n">
-        <v>-1.336183858899054e-05</v>
+        <v>0.0002519474139713346</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0003380295777029196</v>
+        <v>0.002458171169996842</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.002765827748743965</v>
+        <v>0.0049966960283442</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.002188623116887958</v>
+        <v>0.001859881566451255</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.00116476445457194</v>
+        <v>0.001976311210737694</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0.0002236584551055437</v>
+        <v>0.00196757097873054</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0001426433062351656</v>
+        <v>0.001747860660186307</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0003166226912928921</v>
+        <v>0.0006914633326752517</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002107521572377363</v>
+        <v>0.0008647765836193672</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.000991476627711696</v>
+        <v>0.001318858095699152</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0002805986103688068</v>
+        <v>0.005624336893831264</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0003365282035140194</v>
+        <v>0.0007484254127972323</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.000101837709482791</v>
+        <v>0.0003419935023137949</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0003650867205084368</v>
+        <v>0.0001973973990362615</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.000755842241914112</v>
+        <v>0.002907229997139093</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0002487562189054715</v>
+        <v>0.0003414446488019168</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0002841678818715721</v>
+        <v>0.0006340655396633421</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0002616361776896031</v>
+        <v>0.002452816171552383</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0005161383367063427</v>
+        <v>0.0003464440437040362</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001092297605663145</v>
+        <v>0.002507416595979661</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0004250386398763434</v>
+        <v>0.00218880133362302</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0008410804870954469</v>
+        <v>0.001296755802188685</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01295180722891566</v>
+        <v>0.01138554216867472</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01060240963855422</v>
+        <v>0.005060240963855445</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01091897233201585</v>
+        <v>0.006867588932806279</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002337938363443204</v>
+        <v>0.003134962805525998</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004594861660079097</v>
+        <v>0.004096385542168702</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01314229249011863</v>
+        <v>0.01126482213438731</v>
       </c>
       <c r="I9" t="n">
-        <v>5.277044854881119e-05</v>
+        <v>0.0004221635883904895</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01614457831325302</v>
+        <v>0.005500982318271152</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03571033720287455</v>
+        <v>0.02025117739403456</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02857932559425095</v>
+        <v>0.024123495552067</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01304347826086959</v>
+        <v>0.006521739130434745</v>
       </c>
       <c r="N9" t="n">
-        <v>0.008674698795180725</v>
+        <v>0.005120481927710885</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002799607072691568</v>
+        <v>0.003536345776031458</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02564229249011861</v>
+        <v>0.02542841348811493</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01916537867078828</v>
+        <v>0.0162650602409639</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00810412573673871</v>
+        <v>0.007514734774066834</v>
       </c>
       <c r="S9" t="n">
-        <v>0.006373517786561311</v>
+        <v>0.006620553359683779</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01180830039525694</v>
+        <v>0.01240118577075094</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01036144578313253</v>
+        <v>0.007071240105540888</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0004221635883904895</v>
+        <v>0.000104657247514417</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01012845849802375</v>
+        <v>0.007796964939822082</v>
       </c>
       <c r="X9" t="n">
-        <v>0.008554216867469867</v>
+        <v>0.0074406332453826</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.005602409638554217</v>
+        <v>0.003614457831325357</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001912858660998951</v>
+        <v>0.005313496280552577</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003040353786622429</v>
+        <v>0.00951115834218913</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0001807228915662651</v>
+        <v>0.001055408970976224</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0137845849802372</v>
+        <v>0.009404888416578083</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.005844793713163066</v>
+        <v>0.005065963060685985</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.003781925343811421</v>
+        <v>0.002744063324538237</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.00474308300395262</v>
+        <v>0.005494505494505508</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.00057561486132921</v>
+        <v>0.001271420674405743</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0003952569169960895</v>
+        <v>0.001050304035378657</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.007409638554216879</v>
+        <v>0.007651715039577811</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.003732809430255446</v>
+        <v>0.008289054197662038</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0007186290768380288</v>
+        <v>0.0001473477406679913</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.001952506596306103</v>
+        <v>0.0006332453825857343</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.006927710843373514</v>
+        <v>0.006376195536663076</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.002145473574045054</v>
+        <v>0.007071240105540865</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001432806324110691</v>
+        <v>0.001679841897233158</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.004397590361445792</v>
+        <v>0.005023547880690771</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.001965993623804496</v>
+        <v>0.00955145118733508</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.005361445783132535</v>
+        <v>0.006122448979591855</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.002930402930402987</v>
+        <v>0.005171503957783629</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01321171918186849</v>
+        <v>0.01487154150197624</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.006807387862796865</v>
+        <v>0.0009942438513867446</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.003373493975903619</v>
+        <v>0.003957783641160939</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0003091190108191588</v>
+        <v>0.0001473477406680024</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.007590361445783134</v>
+        <v>0.007810026385224256</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.006620553359683845</v>
+        <v>0.002137894174238419</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01359867330016589</v>
+        <v>0.003063241106719328</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01299060254284139</v>
+        <v>0.01773715415019759</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0001964636542239884</v>
+        <v>0.0004782146652497099</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.00057561486132921</v>
+        <v>0.001271420674405743</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.000523286237571996</v>
+        <v>0.01383399209486161</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.01000552791597572</v>
+        <v>0.01774461028192363</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.004644268774703597</v>
+        <v>0.005662650602409692</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0006802721088435715</v>
+        <v>0.0003188097768331288</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.001846965699208469</v>
+        <v>0.005488126649076508</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.008654353562005279</v>
+        <v>0.008058608058608063</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>0.0005804749340369231</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.001160949868073902</v>
+        <v>0.008654353562005269</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.007020453289109973</v>
+        <v>0.01580983969043663</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.006966403162055402</v>
+        <v>0.01332227750138192</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.01373493975903615</v>
+        <v>0.008674698795180758</v>
       </c>
       <c r="BQ9" t="n">
+        <v>9.823182711199419e-05</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.003474078033137395</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.01060240963855427</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.007241569928137059</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.002993051843933769</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.004960422163588352</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.009759036144578325</v>
+      </c>
+      <c r="BX9" t="n">
         <v>0.0002110817941952448</v>
       </c>
-      <c r="BR9" t="n">
-        <v>0.007771084337349399</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0.01222891566265061</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.0007905138339921236</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0.01807228915662651</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.01391566265060242</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0.02150602409638554</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>5.277044854881119e-05</v>
-      </c>
       <c r="BY9" t="n">
-        <v>0.0006626506024096423</v>
+        <v>0.002542841348811486</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.001927710843373498</v>
+        <v>0.00162650602409643</v>
       </c>
       <c r="CA9" t="n">
         <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002874516307352115</v>
+        <v>0.000540275049115957</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.02126506024096386</v>
+        <v>0.01427710843373498</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>0.0005277044854881119</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.002951807228915671</v>
+        <v>0.0009620523784073187</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.01463855421686747</v>
+        <v>0.004819277108433773</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01072289156626508</v>
+        <v>0.01216867469879521</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001333992094861691</v>
+        <v>0.0006633499170812463</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.005361445783132524</v>
+        <v>0.01102409638554223</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.02162650602409637</v>
+        <v>0.01174698795180725</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.00221635883905017</v>
+        <v>0.003693931398416872</v>
       </c>
     </row>
   </sheetData>
